--- a/SubRES_TMPL/SubRES_SUP_Hydrogen.xlsx
+++ b/SubRES_TMPL/SubRES_SUP_Hydrogen.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rbsul\Documents\GitHub\times-ireland-model\SubRES_TMPL\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\VEDA\Demo_models\Demo_models\TIM-LEAF 080626\TIM-LEAF 080626\tim-leaf 080626\SubRES_TMPL\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64455B47-3B87-4E8D-9C48-58217D2EB668}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{62F67F8D-DFD4-4ADE-8356-63F780461C4E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="4" xr2:uid="{62F67F8D-DFD4-4ADE-8356-63F780461C4E}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="7" r:id="rId1"/>
